--- a/site/HR-to-Okta-1-1-0-draft/headings.xlsx
+++ b/site/HR-to-Okta-1-1-0-draft/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -658,6 +658,28 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Offboarding</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>h_01M1BMFPGSXV9T70R2G61JXY7D</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0-draft/#h_01M1BMFPGSXV9T70R2G61JXY7D</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-to-Okta-1-1-0-draft/headings.xlsx
+++ b/site/HR-to-Okta-1-1-0-draft/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:D17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,6 +680,116 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Notifications</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>h_01KXJ4J3ANKKT3JZTNY97SZ39P</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0-draft/#h_01KXJ4J3ANKKT3JZTNY97SZ39P</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Writeback</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>h_01M5W04AJ5432C3NMT4SS7RWNS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0-draft/#h_01M5W04AJ5432C3NMT4SS7RWNS</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>h_01KYHK6HW10A336RAHCBZHHX4P</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0-draft/#h_01KYHK6HW10A336RAHCBZHHX4P</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Attribute Map</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>h_01KXJB70WVXPF13YB3DJ9DHY9F</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0-draft/#h_01KXJB70WVXPF13YB3DJ9DHY9F</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Preview Employee Data</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>h_01KXJB70WV47G9BH5Y2MQ59DD9</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0-draft/#h_01KXJB70WV47G9BH5Y2MQ59DD9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/site/HR-to-Okta-1-1-0-draft/headings.xlsx
+++ b/site/HR-to-Okta-1-1-0-draft/headings.xlsx
@@ -715,12 +715,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01M5W04AJ5432C3NMT4SS7RWNS</t>
+          <t>h_01M5W4RFNHVTRNJ00MRZE54XK9</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0-draft/#h_01M5W04AJ5432C3NMT4SS7RWNS</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/HR-to-Okta-1-1-0-draft/#h_01M5W4RFNHVTRNJ00MRZE54XK9</t>
         </is>
       </c>
     </row>
